--- a/real_data/result_table_2para.xlsx
+++ b/real_data/result_table_2para.xlsx
@@ -407,22 +407,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>0.987465539520758</v>
+        <v>0.987437332558759</v>
       </c>
       <c r="C2" t="n">
-        <v>0.286407960112797</v>
+        <v>0.286397920869819</v>
       </c>
       <c r="D2" t="n">
-        <v>3.44775871149622</v>
+        <v>3.44778107871668</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000565258766125835</v>
+        <v>0.00056521196057439</v>
       </c>
       <c r="F2" t="n">
-        <v>0.426105937699675</v>
+        <v>0.426097407653913</v>
       </c>
       <c r="G2" t="n">
-        <v>1.54882514134184</v>
+        <v>1.5487772574636</v>
       </c>
     </row>
     <row r="3">
@@ -430,22 +430,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.52936676459128</v>
+        <v>-1.52944461068749</v>
       </c>
       <c r="C3" t="n">
-        <v>0.522019913464491</v>
+        <v>0.522018400808726</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.929709624373</v>
+        <v>-2.92986723900543</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00339278885898316</v>
+        <v>0.00339106850246658</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.55252579498168</v>
+        <v>-2.55260067627259</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.506207734200879</v>
+        <v>-0.506288545102388</v>
       </c>
     </row>
     <row r="4">
@@ -453,22 +453,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>1.28318541827097</v>
+        <v>1.28330539152598</v>
       </c>
       <c r="C4" t="n">
-        <v>0.63301311263098</v>
+        <v>0.633005798658729</v>
       </c>
       <c r="D4" t="n">
-        <v>2.02710716834553</v>
+        <v>2.02732011972903</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04265145394472</v>
+        <v>0.0426296852053429</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0424797175142524</v>
+        <v>0.0426140261548762</v>
       </c>
       <c r="G4" t="n">
-        <v>2.52389111902769</v>
+        <v>2.52399675689709</v>
       </c>
     </row>
     <row r="5">
@@ -476,22 +476,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>-2.24716316187053</v>
+        <v>-2.24706527649319</v>
       </c>
       <c r="C5" t="n">
-        <v>0.747681526343997</v>
+        <v>0.747657669836031</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.0055084721147</v>
+        <v>-3.00547345014998</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00265137209747129</v>
+        <v>0.00265167744525333</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.71261895350477</v>
+        <v>-3.71247430937181</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.781707370236298</v>
+        <v>-0.781656243614572</v>
       </c>
     </row>
     <row r="6">
@@ -499,22 +499,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>-3.15181675956082</v>
+        <v>-3.15182797990293</v>
       </c>
       <c r="C6" t="n">
-        <v>0.498651179835985</v>
+        <v>0.498637444512334</v>
       </c>
       <c r="D6" t="n">
-        <v>-6.32068445240119</v>
+        <v>-6.32088106216213</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000000000260407290663448</v>
+        <v>0.000000000260076148404021</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.12917307203935</v>
+        <v>-4.12915737114711</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.17446044708229</v>
+        <v>-2.17449858865876</v>
       </c>
     </row>
     <row r="7">
@@ -525,19 +525,19 @@
         <v>-4.60517018598809</v>
       </c>
       <c r="C7" t="n">
-        <v>0.556595052456532</v>
+        <v>0.556578675561015</v>
       </c>
       <c r="D7" t="n">
-        <v>-8.27382522655057</v>
+        <v>-8.27406867743579</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000000000000000129728283221326</v>
+        <v>0.000000000000000129463529154487</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.69609648880289</v>
+        <v>-5.69606439008768</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.51424388317329</v>
+        <v>-3.5142759818885</v>
       </c>
     </row>
   </sheetData>
